--- a/80_企画書/提案.xlsx
+++ b/80_企画書/提案.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\rock\Workspace\41_Parks-Project\80_企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B69F87-A5E9-46FF-8FCB-2FA88C053173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEA1BE0-0293-4EBE-BE26-FA4E931C0511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="1665" windowWidth="23070" windowHeight="13110" activeTab="2" xr2:uid="{4DD7FBBD-E0AB-4D14-B429-2A1410955B36}"/>
+    <workbookView xWindow="7590" yWindow="2025" windowWidth="23070" windowHeight="13110" activeTab="2" xr2:uid="{4DD7FBBD-E0AB-4D14-B429-2A1410955B36}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,18 +27,429 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Music Files</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Parksは全て大文字</t>
-    <rPh sb="6" eb="7">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>オオモジ</t>
+    <t>セットで提供できるので経験の浅いエンジニアにも経験を積ませることが出来る</t>
+    <rPh sb="4" eb="6">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>男性の写真は不要。</t>
+    <rPh sb="0" eb="2">
+      <t>ダンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>握手しているその部分だけの画像があるとベスト</t>
+    <rPh sb="0" eb="2">
+      <t>アクシュ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変更したのでそのまま使って欲しい</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いちばん右のブロック（３項目）に以下の１項目を加えて４項目として欲しい</t>
+    <rPh sb="4" eb="5">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．お客様の目線で履歴書とスキルシートを作成</t>
+    <rPh sb="3" eb="5">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>メセン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>リレキショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３．エンジニアが応募する</t>
+    <rPh sb="8" eb="10">
+      <t>オウボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４．面談予定が入る⇒面談の主眼点・注意点などを提案</t>
+    <rPh sb="2" eb="4">
+      <t>メンダン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メンダン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュガン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>チュウイテン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．案件が届き、自動でエンジニアを探して案件を配分</t>
+    <rPh sb="2" eb="4">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハイブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>写真を除く３コマでは足りない。</t>
+    <rPh sb="0" eb="2">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここにこのシステムの利便性をうたいたい</t>
+    <rPh sb="10" eb="13">
+      <t>リベンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒お客様にアピールする書類にブラッシュアップして面談の確度を高める</t>
+    <rPh sb="2" eb="4">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショルイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>メンダン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒即時に適材適所を判断、SES側からも追加要求が可能</t>
+    <rPh sb="1" eb="3">
+      <t>ソクジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テキザイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テキショ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒誤字脱字など内容のチェック</t>
+    <rPh sb="1" eb="3">
+      <t>ゴジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダツジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⇒案件メールをもとにお客様の要求を分析、面談で的確な受け答えができるよスクリプトを作成</t>
+    <rPh sb="1" eb="3">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メンダン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキカク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下がこのシステムの特徴なので、存分に魅力が伝わるように構成して欲しい</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゾンブン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ミリョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>５ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>４ページ目に集約されるので不要</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウヤク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もしくは４ページ目を２ページに分割する</t>
+    <rPh sb="8" eb="9">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブンカツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>６ページ目</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あくまで現状（案）であることを強調する</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>写真上に初期費用の７％があるが、月額３％の方が良い</t>
+    <rPh sb="0" eb="1">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲツガク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運用の約束に「守秘義務」を入れる</t>
+    <rPh sb="0" eb="2">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュヒ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ギム</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文言は考えて</t>
+    <rPh sb="0" eb="2">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カンガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1817,21 +2228,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>229876</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>181698</xdr:rowOff>
+      <xdr:colOff>210824</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>134067</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B393C397-9FF9-F1FA-C91E-E70206EC03A8}"/>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{817BBBE4-665B-E195-50F4-27E6881AA80D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1847,8 +2258,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9145276" cy="5182323"/>
+          <a:off x="0" y="10953750"/>
+          <a:ext cx="9126224" cy="5134692"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1861,21 +2272,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>220350</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>143593</xdr:rowOff>
+      <xdr:colOff>201297</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>172172</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41C8ADD-D111-CF09-54E0-31D0CB9BB860}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE1523F8-3846-7964-D74F-D5C1A99C29A4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1891,8 +2302,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5476875"/>
-          <a:ext cx="9135750" cy="5144218"/>
+          <a:off x="0" y="16430625"/>
+          <a:ext cx="9116697" cy="5172797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1905,21 +2316,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>210824</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>134067</xdr:rowOff>
+      <xdr:colOff>220350</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>172172</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{817BBBE4-665B-E195-50F4-27E6881AA80D}"/>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8272F9F6-4100-FCD6-DDFA-8287C2BD7C0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1935,8 +2346,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="10953750"/>
-          <a:ext cx="9126224" cy="5134692"/>
+          <a:off x="0" y="21907500"/>
+          <a:ext cx="9135750" cy="5172797"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1949,21 +2360,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>201297</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>172172</xdr:rowOff>
+      <xdr:colOff>210824</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>124540</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE1523F8-3846-7964-D74F-D5C1A99C29A4}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F350963-71EB-FF01-37F4-CA41B337FB26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1973,94 +2384,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="16430625"/>
-          <a:ext cx="9116697" cy="5172797"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>220350</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>172172</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8272F9F6-4100-FCD6-DDFA-8287C2BD7C0C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="21907500"/>
-          <a:ext cx="9135750" cy="5172797"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>210824</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>124540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F350963-71EB-FF01-37F4-CA41B337FB26}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2438,12 +2761,139 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650C5238-E5E8-44FF-A8BF-185371004620}">
-  <dimension ref="O7"/>
+  <dimension ref="A5:I28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="7" spans="15:15" x14ac:dyDescent="0.4">
-      <c r="O7" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
